--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/28. location_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/28. location_wip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\dml\city location institution\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1181ED0-304B-44C6-8CF8-E1B67C4BEB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA5F5F6-EA9F-43D6-8805-D6B86FCC9ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="708" windowWidth="12108" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1852" uniqueCount="1370">
   <si>
     <t>street_name</t>
   </si>
@@ -2122,6 +2122,2022 @@
   </si>
   <si>
     <t>SCE</t>
+  </si>
+  <si>
+    <t>Barbu Văcărescu</t>
+  </si>
+  <si>
+    <t>020276</t>
+  </si>
+  <si>
+    <t>Bd. Dimitrie Pompeiu</t>
+  </si>
+  <si>
+    <t>020335</t>
+  </si>
+  <si>
+    <t>Calea Florești</t>
+  </si>
+  <si>
+    <t>400394</t>
+  </si>
+  <si>
+    <t>Str. Constanța</t>
+  </si>
+  <si>
+    <t>400158</t>
+  </si>
+  <si>
+    <t>Bd. Iuliu Maniu</t>
+  </si>
+  <si>
+    <t>061103</t>
+  </si>
+  <si>
+    <t>Str. Tudor Arghezi</t>
+  </si>
+  <si>
+    <t>010961</t>
+  </si>
+  <si>
+    <t>Str. Frunzișului</t>
+  </si>
+  <si>
+    <t>400664</t>
+  </si>
+  <si>
+    <t>Bd. Unirii</t>
+  </si>
+  <si>
+    <t>030833</t>
+  </si>
+  <si>
+    <t>Str. Vasile Lascăr</t>
+  </si>
+  <si>
+    <t>020492</t>
+  </si>
+  <si>
+    <t>Bd. Timișoara</t>
+  </si>
+  <si>
+    <t>061331</t>
+  </si>
+  <si>
+    <t>Calea Floreasca</t>
+  </si>
+  <si>
+    <t>014476</t>
+  </si>
+  <si>
+    <t>Str. Someșului</t>
+  </si>
+  <si>
+    <t>400145</t>
+  </si>
+  <si>
+    <t>Bd. Tudor Vladimirescu</t>
+  </si>
+  <si>
+    <t>050881</t>
+  </si>
+  <si>
+    <t>Str. Nicolae Filipescu</t>
+  </si>
+  <si>
+    <t>020961</t>
+  </si>
+  <si>
+    <t>Str. Henri Barbusse</t>
+  </si>
+  <si>
+    <t>011317</t>
+  </si>
+  <si>
+    <t>Str. Piatra Morii</t>
+  </si>
+  <si>
+    <t>Bd. Corneliu Coposu</t>
+  </si>
+  <si>
+    <t>030167</t>
+  </si>
+  <si>
+    <t>Str. Gheorghe Țițeica</t>
+  </si>
+  <si>
+    <t>900178</t>
+  </si>
+  <si>
+    <t>Str. Brașov</t>
+  </si>
+  <si>
+    <t>061344</t>
+  </si>
+  <si>
+    <t>Bd. Preciziei</t>
+  </si>
+  <si>
+    <t>062203</t>
+  </si>
+  <si>
+    <t>Str. Inandului</t>
+  </si>
+  <si>
+    <t>300714</t>
+  </si>
+  <si>
+    <t>Bd. Barbu Văcărescu</t>
+  </si>
+  <si>
+    <t>Bd. Lascăr Catargiu</t>
+  </si>
+  <si>
+    <t>010665</t>
+  </si>
+  <si>
+    <t>Str. George Constantinescu</t>
+  </si>
+  <si>
+    <t>020339</t>
+  </si>
+  <si>
+    <t>Str. Dimitrie Pompeiu</t>
+  </si>
+  <si>
+    <t>Str. Pechea</t>
+  </si>
+  <si>
+    <t>021424</t>
+  </si>
+  <si>
+    <t>Str. Drumul Osiei</t>
+  </si>
+  <si>
+    <t>062395</t>
+  </si>
+  <si>
+    <t>Str. Buzești</t>
+  </si>
+  <si>
+    <t>011013</t>
+  </si>
+  <si>
+    <t>Str. Barbu Văcărescu</t>
+  </si>
+  <si>
+    <t>020285</t>
+  </si>
+  <si>
+    <t>Str. Nicolae Caramfil</t>
+  </si>
+  <si>
+    <t>014142</t>
+  </si>
+  <si>
+    <t>010567</t>
+  </si>
+  <si>
+    <t>400616</t>
+  </si>
+  <si>
+    <t>Str. Frumoasă</t>
+  </si>
+  <si>
+    <t>010986</t>
+  </si>
+  <si>
+    <t>061072</t>
+  </si>
+  <si>
+    <t>Str. Take Ionescu</t>
+  </si>
+  <si>
+    <t>300124</t>
+  </si>
+  <si>
+    <t>Str. Dorobanților</t>
+  </si>
+  <si>
+    <t>400609</t>
+  </si>
+  <si>
+    <t>Bd. 21 Decembrie 1989</t>
+  </si>
+  <si>
+    <t>400124</t>
+  </si>
+  <si>
+    <t>Str. Calea Martirilor</t>
+  </si>
+  <si>
+    <t>300725</t>
+  </si>
+  <si>
+    <t>062204</t>
+  </si>
+  <si>
+    <t>Str. Preciziei</t>
+  </si>
+  <si>
+    <t>Șos. Virtuții</t>
+  </si>
+  <si>
+    <t>060787</t>
+  </si>
+  <si>
+    <t>Str. Avrig</t>
+  </si>
+  <si>
+    <t>021578</t>
+  </si>
+  <si>
+    <t>Str. București</t>
+  </si>
+  <si>
+    <t>400613</t>
+  </si>
+  <si>
+    <t>Bd. Vasile Milea</t>
+  </si>
+  <si>
+    <t>Str. Rahovei</t>
+  </si>
+  <si>
+    <t>550057</t>
+  </si>
+  <si>
+    <t>Str. Delea Nouă</t>
+  </si>
+  <si>
+    <t>030925</t>
+  </si>
+  <si>
+    <t>Str. Polonă</t>
+  </si>
+  <si>
+    <t>010503</t>
+  </si>
+  <si>
+    <t>062202</t>
+  </si>
+  <si>
+    <t>Str. Mitropoliei</t>
+  </si>
+  <si>
+    <t>720005</t>
+  </si>
+  <si>
+    <t>Str. Louis Pasteur</t>
+  </si>
+  <si>
+    <t>410154</t>
+  </si>
+  <si>
+    <t>Str. Delea Veche</t>
+  </si>
+  <si>
+    <t>024102</t>
+  </si>
+  <si>
+    <t>Str. Sfântul Lazăr</t>
+  </si>
+  <si>
+    <t>700259</t>
+  </si>
+  <si>
+    <t>020337</t>
+  </si>
+  <si>
+    <t>Str. Republicii</t>
+  </si>
+  <si>
+    <t>400489</t>
+  </si>
+  <si>
+    <t>Str. Universității</t>
+  </si>
+  <si>
+    <t>700115</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>050883</t>
+  </si>
+  <si>
+    <t>Str. Vasile Alecsandri</t>
+  </si>
+  <si>
+    <t>300078</t>
+  </si>
+  <si>
+    <t>Str. Petru Rareș</t>
+  </si>
+  <si>
+    <t>400165</t>
+  </si>
+  <si>
+    <t>Bd. Iancu de Hunedoara</t>
+  </si>
+  <si>
+    <t>011745</t>
+  </si>
+  <si>
+    <t>Str. Gheorghe Doja</t>
+  </si>
+  <si>
+    <t>540015</t>
+  </si>
+  <si>
+    <t>Str. Paris</t>
+  </si>
+  <si>
+    <t>011815</t>
+  </si>
+  <si>
+    <t>Str. Palat</t>
+  </si>
+  <si>
+    <t>700019</t>
+  </si>
+  <si>
+    <t>Str. Morilor</t>
+  </si>
+  <si>
+    <t>550197</t>
+  </si>
+  <si>
+    <t>Str. Henri Coandă</t>
+  </si>
+  <si>
+    <t>400349</t>
+  </si>
+  <si>
+    <t>Str. Fabrica de Glucoză</t>
+  </si>
+  <si>
+    <t>020331</t>
+  </si>
+  <si>
+    <t>Str. Sfântul Andrei</t>
+  </si>
+  <si>
+    <t>700028</t>
+  </si>
+  <si>
+    <t>Str. Bolyai</t>
+  </si>
+  <si>
+    <t>540054</t>
+  </si>
+  <si>
+    <t>Str. Constantin Brâncuși</t>
+  </si>
+  <si>
+    <t>400458</t>
+  </si>
+  <si>
+    <t>Str. Observatorului</t>
+  </si>
+  <si>
+    <t>400363</t>
+  </si>
+  <si>
+    <t>011015</t>
+  </si>
+  <si>
+    <t>Str. Bună Ziua</t>
+  </si>
+  <si>
+    <t>400495</t>
+  </si>
+  <si>
+    <t>Str. Independenței</t>
+  </si>
+  <si>
+    <t>700111</t>
+  </si>
+  <si>
+    <t>Str. Calea Aradului</t>
+  </si>
+  <si>
+    <t>300088</t>
+  </si>
+  <si>
+    <t>Str. 22 Decembrie</t>
+  </si>
+  <si>
+    <t>540124</t>
+  </si>
+  <si>
+    <t>010494</t>
+  </si>
+  <si>
+    <t>Str. Traian Vuia</t>
+  </si>
+  <si>
+    <t>400397</t>
+  </si>
+  <si>
+    <t>Str. Metalurgiei</t>
+  </si>
+  <si>
+    <t>041832</t>
+  </si>
+  <si>
+    <t>Str. Decebal</t>
+  </si>
+  <si>
+    <t>410215</t>
+  </si>
+  <si>
+    <t>Str. Mihai Viteazul</t>
+  </si>
+  <si>
+    <t>500174</t>
+  </si>
+  <si>
+    <t>Str. Vasile Lupu</t>
+  </si>
+  <si>
+    <t>700309</t>
+  </si>
+  <si>
+    <t>Str. Gheorghe Lazăr</t>
+  </si>
+  <si>
+    <t>300080</t>
+  </si>
+  <si>
+    <t>Str. Cuza Vodă</t>
+  </si>
+  <si>
+    <t>540098</t>
+  </si>
+  <si>
+    <t>Str. Aurel Vlaicu</t>
+  </si>
+  <si>
+    <t>400581</t>
+  </si>
+  <si>
+    <t>Str. Turnu Măgurele</t>
+  </si>
+  <si>
+    <t>041714</t>
+  </si>
+  <si>
+    <t>Str. Tudor Vladimirescu</t>
+  </si>
+  <si>
+    <t>410203</t>
+  </si>
+  <si>
+    <t>Str. Iuliu Maniu</t>
+  </si>
+  <si>
+    <t>500091</t>
+  </si>
+  <si>
+    <t>Str. Fabrica de Chibrituri</t>
+  </si>
+  <si>
+    <t>050483</t>
+  </si>
+  <si>
+    <t>Str. Circumvalațiunii</t>
+  </si>
+  <si>
+    <t>300012</t>
+  </si>
+  <si>
+    <t>Str. Livezeni</t>
+  </si>
+  <si>
+    <t>540225</t>
+  </si>
+  <si>
+    <t>Str. Aviației</t>
+  </si>
+  <si>
+    <t>014192</t>
+  </si>
+  <si>
+    <t>Str. Oașului</t>
+  </si>
+  <si>
+    <t>400264</t>
+  </si>
+  <si>
+    <t>Str. Calea Clujului</t>
+  </si>
+  <si>
+    <t>410221</t>
+  </si>
+  <si>
+    <t>Str. Zizinului</t>
+  </si>
+  <si>
+    <t>500414</t>
+  </si>
+  <si>
+    <t>Str. Ion Mihalache</t>
+  </si>
+  <si>
+    <t>011171</t>
+  </si>
+  <si>
+    <t>Bd. Gheorghe Magheru</t>
+  </si>
+  <si>
+    <t>010325</t>
+  </si>
+  <si>
+    <t>Str. Lipscani</t>
+  </si>
+  <si>
+    <t>030037</t>
+  </si>
+  <si>
+    <t>Str. Grigore Alexandrescu</t>
+  </si>
+  <si>
+    <t>010623</t>
+  </si>
+  <si>
+    <t>Str. Calea Șagului</t>
+  </si>
+  <si>
+    <t>300516</t>
+  </si>
+  <si>
+    <t>Str. Valea Lupului</t>
+  </si>
+  <si>
+    <t>707410</t>
+  </si>
+  <si>
+    <t>Bd. Mircea Vodă</t>
+  </si>
+  <si>
+    <t>030667</t>
+  </si>
+  <si>
+    <t>Str. Valea Cascadelor</t>
+  </si>
+  <si>
+    <t>061511</t>
+  </si>
+  <si>
+    <t>Bd. Ion Mihalache</t>
+  </si>
+  <si>
+    <t>Bd. Theodor Pallady</t>
+  </si>
+  <si>
+    <t>032258</t>
+  </si>
+  <si>
+    <t>Șos. București‑Nord</t>
+  </si>
+  <si>
+    <t>077190</t>
+  </si>
+  <si>
+    <t>Str. Industriilor</t>
+  </si>
+  <si>
+    <t>500464</t>
+  </si>
+  <si>
+    <t>Șos. Chitilei</t>
+  </si>
+  <si>
+    <t>012393</t>
+  </si>
+  <si>
+    <t>Str. Gherghiței</t>
+  </si>
+  <si>
+    <t>022441</t>
+  </si>
+  <si>
+    <t>061104</t>
+  </si>
+  <si>
+    <t>Str. Dr. Felix</t>
+  </si>
+  <si>
+    <t>540099</t>
+  </si>
+  <si>
+    <t>Str. Fabricii</t>
+  </si>
+  <si>
+    <t>400632</t>
+  </si>
+  <si>
+    <t>Str. Traian</t>
+  </si>
+  <si>
+    <t>300599</t>
+  </si>
+  <si>
+    <t>Str. Depozitelor</t>
+  </si>
+  <si>
+    <t>200746</t>
+  </si>
+  <si>
+    <t>550132</t>
+  </si>
+  <si>
+    <t>Str. Jiului</t>
+  </si>
+  <si>
+    <t>013218</t>
+  </si>
+  <si>
+    <t>510134</t>
+  </si>
+  <si>
+    <t>Str. Șoseaua Sibiului</t>
+  </si>
+  <si>
+    <t>557260</t>
+  </si>
+  <si>
+    <t>Str. Râmnicu Sărat</t>
+  </si>
+  <si>
+    <t>240475</t>
+  </si>
+  <si>
+    <t>Str. Tăietura Turcului</t>
+  </si>
+  <si>
+    <t>400221</t>
+  </si>
+  <si>
+    <t>Str. Condorilor</t>
+  </si>
+  <si>
+    <t>600302</t>
+  </si>
+  <si>
+    <t>Str. Aviatorilor</t>
+  </si>
+  <si>
+    <t>200390</t>
+  </si>
+  <si>
+    <t>Str. Șoseaua Mediașului</t>
+  </si>
+  <si>
+    <t>010626</t>
+  </si>
+  <si>
+    <t>Calea Bucureștilor</t>
+  </si>
+  <si>
+    <t>075100</t>
+  </si>
+  <si>
+    <t>Calea Giulești</t>
+  </si>
+  <si>
+    <t>060274</t>
+  </si>
+  <si>
+    <t>Str. Constantin Silvestri</t>
+  </si>
+  <si>
+    <t>060041</t>
+  </si>
+  <si>
+    <t>Str. Dinicu Golescu</t>
+  </si>
+  <si>
+    <t>010873</t>
+  </si>
+  <si>
+    <t>300003</t>
+  </si>
+  <si>
+    <t>Str. Erou Iancu Nicolae</t>
+  </si>
+  <si>
+    <t>Str. Logofătul Tăutu</t>
+  </si>
+  <si>
+    <t>031212</t>
+  </si>
+  <si>
+    <t>Str. Aeroportului</t>
+  </si>
+  <si>
+    <t>600324</t>
+  </si>
+  <si>
+    <t>Str. Calea Timișoarei</t>
+  </si>
+  <si>
+    <t>300701</t>
+  </si>
+  <si>
+    <t>Str. Chimiei</t>
+  </si>
+  <si>
+    <t>600291</t>
+  </si>
+  <si>
+    <t>Str. Piața Gării</t>
+  </si>
+  <si>
+    <t>620033</t>
+  </si>
+  <si>
+    <t>Calea Dorobanților</t>
+  </si>
+  <si>
+    <t>400117</t>
+  </si>
+  <si>
+    <t>Str. Incintă Port</t>
+  </si>
+  <si>
+    <t>900900</t>
+  </si>
+  <si>
+    <t>550234</t>
+  </si>
+  <si>
+    <t>Str. Șoseaua Brăilei</t>
+  </si>
+  <si>
+    <t>800303</t>
+  </si>
+  <si>
+    <t>Bd. General Vasile Milea</t>
+  </si>
+  <si>
+    <t>500407</t>
+  </si>
+  <si>
+    <t>Str. Cavafii Vechi</t>
+  </si>
+  <si>
+    <t>Bd. Expoziției</t>
+  </si>
+  <si>
+    <t>012101</t>
+  </si>
+  <si>
+    <t>547185</t>
+  </si>
+  <si>
+    <t>Str. Daniel Danielopolu</t>
+  </si>
+  <si>
+    <t>014134</t>
+  </si>
+  <si>
+    <t>Bd. Bucureștii Noi</t>
+  </si>
+  <si>
+    <t>012364</t>
+  </si>
+  <si>
+    <t>Str. Dr. Aurel Păunescu Podeanu</t>
+  </si>
+  <si>
+    <t>300587</t>
+  </si>
+  <si>
+    <t>Str. Tăuțiului</t>
+  </si>
+  <si>
+    <t>427006</t>
+  </si>
+  <si>
+    <t>300081</t>
+  </si>
+  <si>
+    <t>Str. Constructorilor</t>
+  </si>
+  <si>
+    <t>600189</t>
+  </si>
+  <si>
+    <t>Str. Navodari</t>
+  </si>
+  <si>
+    <t>905700</t>
+  </si>
+  <si>
+    <t>Str. Siriului</t>
+  </si>
+  <si>
+    <t>014354</t>
+  </si>
+  <si>
+    <t>551130</t>
+  </si>
+  <si>
+    <t>200395</t>
+  </si>
+  <si>
+    <t>077135</t>
+  </si>
+  <si>
+    <t>505600</t>
+  </si>
+  <si>
+    <t>Str. Avram Iancu</t>
+  </si>
+  <si>
+    <t>400089</t>
+  </si>
+  <si>
+    <t>030033</t>
+  </si>
+  <si>
+    <t>011172</t>
+  </si>
+  <si>
+    <t>Str. Drumul Gării Odăi</t>
+  </si>
+  <si>
+    <t>Str. Portului</t>
+  </si>
+  <si>
+    <t>800025</t>
+  </si>
+  <si>
+    <t>607305</t>
+  </si>
+  <si>
+    <t>Str. Calea Moților</t>
+  </si>
+  <si>
+    <t>130087</t>
+  </si>
+  <si>
+    <t>Bd. 1 Decembrie 1918</t>
+  </si>
+  <si>
+    <t>410068</t>
+  </si>
+  <si>
+    <t>Str. Humorului</t>
+  </si>
+  <si>
+    <t>727475</t>
+  </si>
+  <si>
+    <t>Str. Calea Unirii</t>
+  </si>
+  <si>
+    <t>720218</t>
+  </si>
+  <si>
+    <t>Str. Energiei</t>
+  </si>
+  <si>
+    <t>Str. Henry Ford</t>
+  </si>
+  <si>
+    <t>200396</t>
+  </si>
+  <si>
+    <t>Str. Sema Parc</t>
+  </si>
+  <si>
+    <t>060354</t>
+  </si>
+  <si>
+    <t>Piața Constantin Brâncuși</t>
+  </si>
+  <si>
+    <t>410469</t>
+  </si>
+  <si>
+    <t>Str. Theodor Pallady</t>
+  </si>
+  <si>
+    <t>077096</t>
+  </si>
+  <si>
+    <t>Str. Calea Turzii</t>
+  </si>
+  <si>
+    <t>Str. Uzinei</t>
+  </si>
+  <si>
+    <t>240050</t>
+  </si>
+  <si>
+    <t>Str. Nicolae Teclu</t>
+  </si>
+  <si>
+    <t>032368</t>
+  </si>
+  <si>
+    <t>Str. Europa</t>
+  </si>
+  <si>
+    <t>430002</t>
+  </si>
+  <si>
+    <t>Str. Fabricii de Zahăr</t>
+  </si>
+  <si>
+    <t>Bd. Mamaia Nord</t>
+  </si>
+  <si>
+    <t>Str. Aleea Industriilor</t>
+  </si>
+  <si>
+    <t>120024</t>
+  </si>
+  <si>
+    <t>115400</t>
+  </si>
+  <si>
+    <t>Str. Gării</t>
+  </si>
+  <si>
+    <t>517385</t>
+  </si>
+  <si>
+    <t>Str. Pitesti</t>
+  </si>
+  <si>
+    <t>230054</t>
+  </si>
+  <si>
+    <t>Str. Anul 1848</t>
+  </si>
+  <si>
+    <t>100559</t>
+  </si>
+  <si>
+    <t>Calea Rahovei</t>
+  </si>
+  <si>
+    <t>050912</t>
+  </si>
+  <si>
+    <t>061126</t>
+  </si>
+  <si>
+    <t>Str. Tufănelelor</t>
+  </si>
+  <si>
+    <t>225200</t>
+  </si>
+  <si>
+    <t>625100</t>
+  </si>
+  <si>
+    <t>Str. Mărășești</t>
+  </si>
+  <si>
+    <t>500085</t>
+  </si>
+  <si>
+    <t>Str. Mihai Bravu</t>
+  </si>
+  <si>
+    <t>100385</t>
+  </si>
+  <si>
+    <t>Str. Cernăuți</t>
+  </si>
+  <si>
+    <t>720043</t>
+  </si>
+  <si>
+    <t>540228</t>
+  </si>
+  <si>
+    <t>515200</t>
+  </si>
+  <si>
+    <t>Str. Victoriei</t>
+  </si>
+  <si>
+    <t>430122</t>
+  </si>
+  <si>
+    <t>Str. Negru Vodă</t>
+  </si>
+  <si>
+    <t>115300</t>
+  </si>
+  <si>
+    <t>011202</t>
+  </si>
+  <si>
+    <t>Str. Principală</t>
+  </si>
+  <si>
+    <t>557105</t>
+  </si>
+  <si>
+    <t>547231</t>
+  </si>
+  <si>
+    <t>Str. Drumul Cetății</t>
+  </si>
+  <si>
+    <t>420006</t>
+  </si>
+  <si>
+    <t>410546</t>
+  </si>
+  <si>
+    <t>Str. Transilvaniei</t>
+  </si>
+  <si>
+    <t>120214</t>
+  </si>
+  <si>
+    <t>Str. Ciucului</t>
+  </si>
+  <si>
+    <t>535600</t>
+  </si>
+  <si>
+    <t>540472</t>
+  </si>
+  <si>
+    <t>032266</t>
+  </si>
+  <si>
+    <t>Str. Stadionului</t>
+  </si>
+  <si>
+    <t>551025</t>
+  </si>
+  <si>
+    <t>Str. Râmnicu Vâlcea</t>
+  </si>
+  <si>
+    <t>240171</t>
+  </si>
+  <si>
+    <t>Str. Hărmanului</t>
+  </si>
+  <si>
+    <t>500240</t>
+  </si>
+  <si>
+    <t>Str. Electroprecizia</t>
+  </si>
+  <si>
+    <t>Str. Calea Chișinăului</t>
+  </si>
+  <si>
+    <t>700177</t>
+  </si>
+  <si>
+    <t>300123</t>
+  </si>
+  <si>
+    <t>Str. Brăilei</t>
+  </si>
+  <si>
+    <t>800320</t>
+  </si>
+  <si>
+    <t>Str. Caracal</t>
+  </si>
+  <si>
+    <t>Str. Industriei</t>
+  </si>
+  <si>
+    <t>420083</t>
+  </si>
+  <si>
+    <t>Str. Redului</t>
+  </si>
+  <si>
+    <t>601075</t>
+  </si>
+  <si>
+    <t>Str. Uzinelor</t>
+  </si>
+  <si>
+    <t>410605</t>
+  </si>
+  <si>
+    <t>Str. Crișan</t>
+  </si>
+  <si>
+    <t>315100</t>
+  </si>
+  <si>
+    <t>Str. Timișoarei</t>
+  </si>
+  <si>
+    <t>305500</t>
+  </si>
+  <si>
+    <t>Str. Calea Domnească</t>
+  </si>
+  <si>
+    <t>130105</t>
+  </si>
+  <si>
+    <t>Str. Poetului</t>
+  </si>
+  <si>
+    <t>310059</t>
+  </si>
+  <si>
+    <t>Buzesti</t>
+  </si>
+  <si>
+    <t>Iuliu Maniu</t>
+  </si>
+  <si>
+    <t>Pipera</t>
+  </si>
+  <si>
+    <t>020112</t>
+  </si>
+  <si>
+    <t>014459</t>
+  </si>
+  <si>
+    <t>Tudor Vladimirescu</t>
+  </si>
+  <si>
+    <t>Vasile Milea</t>
+  </si>
+  <si>
+    <t>Nicolae Caramfil</t>
+  </si>
+  <si>
+    <t>Dimitrie Pompeiu</t>
+  </si>
+  <si>
+    <t>Str. Hella</t>
+  </si>
+  <si>
+    <t>300635</t>
+  </si>
+  <si>
+    <t>Str. Porsche</t>
+  </si>
+  <si>
+    <t>500480</t>
+  </si>
+  <si>
+    <t>Str. ZF Group</t>
+  </si>
+  <si>
+    <t>300678</t>
+  </si>
+  <si>
+    <t>Str. Valeo</t>
+  </si>
+  <si>
+    <t>300712</t>
+  </si>
+  <si>
+    <t>Nicolae Titulescu</t>
+  </si>
+  <si>
+    <t>011132</t>
+  </si>
+  <si>
+    <t>Drumul Osiei</t>
+  </si>
+  <si>
+    <t>Calea Victoriei</t>
+  </si>
+  <si>
+    <t>030023</t>
+  </si>
+  <si>
+    <t>Str. Vasile Lascar</t>
+  </si>
+  <si>
+    <t>Str. Constantin Ghercu</t>
+  </si>
+  <si>
+    <t>020773</t>
+  </si>
+  <si>
+    <t>061334</t>
+  </si>
+  <si>
+    <t>550372</t>
+  </si>
+  <si>
+    <t>Str. Politehnicii</t>
+  </si>
+  <si>
+    <t>300006</t>
+  </si>
+  <si>
+    <t>Dietmar-Hopp-Allee</t>
+  </si>
+  <si>
+    <t>Werner-von-Siemens-Straße</t>
+  </si>
+  <si>
+    <t>Karaportti</t>
+  </si>
+  <si>
+    <t>Torshamnsgatan</t>
+  </si>
+  <si>
+    <t>Quai Marcel Dassault</t>
+  </si>
+  <si>
+    <t>Herengracht</t>
+  </si>
+  <si>
+    <t>1017 CE</t>
+  </si>
+  <si>
+    <t>Regeringsgatan</t>
+  </si>
+  <si>
+    <t>Bijlmerdreef</t>
+  </si>
+  <si>
+    <t>1102 CT</t>
+  </si>
+  <si>
+    <t>Canada Square</t>
+  </si>
+  <si>
+    <t>E14 5HQ</t>
+  </si>
+  <si>
+    <t>Shell Centre</t>
+  </si>
+  <si>
+    <t>SE1 7NA</t>
+  </si>
+  <si>
+    <t>69190</t>
+  </si>
+  <si>
+    <t>80333</t>
+  </si>
+  <si>
+    <t>02610</t>
+  </si>
+  <si>
+    <t>16440</t>
+  </si>
+  <si>
+    <t>92150</t>
+  </si>
+  <si>
+    <t>11153</t>
+  </si>
+  <si>
+    <t>Lindenstrasse</t>
+  </si>
+  <si>
+    <t>6340</t>
+  </si>
+  <si>
+    <t>Sveavägen</t>
+  </si>
+  <si>
+    <t>11134</t>
+  </si>
+  <si>
+    <t>Simon Carmiggeltstraat</t>
+  </si>
+  <si>
+    <t>1011 DJ</t>
+  </si>
+  <si>
+    <t>Itämerenkatu</t>
+  </si>
+  <si>
+    <t>00180</t>
+  </si>
+  <si>
+    <t>Jagiellońska</t>
+  </si>
+  <si>
+    <t>03‑301</t>
+  </si>
+  <si>
+    <t>Gran Vía</t>
+  </si>
+  <si>
+    <t>28013</t>
+  </si>
+  <si>
+    <t>Affolternstrasse</t>
+  </si>
+  <si>
+    <t>8050</t>
+  </si>
+  <si>
+    <t>35 Rue Joseph Monier</t>
+  </si>
+  <si>
+    <t>92500</t>
+  </si>
+  <si>
+    <t>Carrer de Pallars</t>
+  </si>
+  <si>
+    <t>08005</t>
+  </si>
+  <si>
+    <t>Hedeager</t>
+  </si>
+  <si>
+    <t>8200</t>
+  </si>
+  <si>
+    <t>De Run</t>
+  </si>
+  <si>
+    <t>5504 DR</t>
+  </si>
+  <si>
+    <t>110 Fulbourn Road</t>
+  </si>
+  <si>
+    <t>CB1 9NJ</t>
+  </si>
+  <si>
+    <t>Keilasatama</t>
+  </si>
+  <si>
+    <t>02150</t>
+  </si>
+  <si>
+    <t>Valeska-Gert-Straße</t>
+  </si>
+  <si>
+    <t>10243</t>
+  </si>
+  <si>
+    <t>Warfvinges väg</t>
+  </si>
+  <si>
+    <t>11251</t>
+  </si>
+  <si>
+    <t>Provincialeweg</t>
+  </si>
+  <si>
+    <t>1506 MA</t>
+  </si>
+  <si>
+    <t>14 Rue Royale</t>
+  </si>
+  <si>
+    <t>75008</t>
+  </si>
+  <si>
+    <t>Tweede Weteringplantsoen</t>
+  </si>
+  <si>
+    <t>1017 ZD</t>
+  </si>
+  <si>
+    <t>Gropegårdsgatan</t>
+  </si>
+  <si>
+    <t>41715</t>
+  </si>
+  <si>
+    <t>Avenue Nestlé</t>
+  </si>
+  <si>
+    <t>1800</t>
+  </si>
+  <si>
+    <t>High Tech Campus</t>
+  </si>
+  <si>
+    <t>5656 AG</t>
+  </si>
+  <si>
+    <t>39 Chemin du Champ-des-Filles</t>
+  </si>
+  <si>
+    <t>1228</t>
+  </si>
+  <si>
+    <t>Krapinska</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>11 Rue de Tilsitt</t>
+  </si>
+  <si>
+    <t>75017</t>
+  </si>
+  <si>
+    <t>111 Quai du Président Roosevelt</t>
+  </si>
+  <si>
+    <t>92130</t>
+  </si>
+  <si>
+    <t>Am Stadtrand</t>
+  </si>
+  <si>
+    <t>22047</t>
+  </si>
+  <si>
+    <t>Grenzacherstrasse</t>
+  </si>
+  <si>
+    <t>4070</t>
+  </si>
+  <si>
+    <t>Lichtstrasse</t>
+  </si>
+  <si>
+    <t>4056</t>
+  </si>
+  <si>
+    <t>IKEA Hotellvägen</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>Lufthansa Aviation Center</t>
+  </si>
+  <si>
+    <t>60546</t>
+  </si>
+  <si>
+    <t>Einsteinstrasse</t>
+  </si>
+  <si>
+    <t>81677</t>
+  </si>
+  <si>
+    <t>Georg-Brauchle-Ring</t>
+  </si>
+  <si>
+    <t>80992</t>
+  </si>
+  <si>
+    <t>Arkadiankatu</t>
+  </si>
+  <si>
+    <t>1 Francis Crick Avenue</t>
+  </si>
+  <si>
+    <t>CB2 0AA</t>
+  </si>
+  <si>
+    <t>Baarermattstrasse</t>
+  </si>
+  <si>
+    <t>Oranienburger Strasse</t>
+  </si>
+  <si>
+    <t>10117</t>
+  </si>
+  <si>
+    <t>Carl-Bosch-Strasse</t>
+  </si>
+  <si>
+    <t>67056</t>
+  </si>
+  <si>
+    <t>Mäster Samuelsgatan</t>
+  </si>
+  <si>
+    <t>11121</t>
+  </si>
+  <si>
+    <t>J.C. Jacobsens Gade</t>
+  </si>
+  <si>
+    <t>1799</t>
+  </si>
+  <si>
+    <t>Werner-von-Siemens-Strasse</t>
+  </si>
+  <si>
+    <t>Tour Carpe Diem</t>
+  </si>
+  <si>
+    <t>92400</t>
+  </si>
+  <si>
+    <t>Moor Lane</t>
+  </si>
+  <si>
+    <t>DE24 8BJ</t>
+  </si>
+  <si>
+    <t>1 St James’s Square</t>
+  </si>
+  <si>
+    <t>SW1Y 4PD</t>
+  </si>
+  <si>
+    <t>Esplanaden</t>
+  </si>
+  <si>
+    <t>1098</t>
+  </si>
+  <si>
+    <t>Vodafone House</t>
+  </si>
+  <si>
+    <t>RG14 2FN</t>
+  </si>
+  <si>
+    <t>10 Rue Marcel Dassault</t>
+  </si>
+  <si>
+    <t>78140</t>
+  </si>
+  <si>
+    <t>1 Churchill Place</t>
+  </si>
+  <si>
+    <t>E14 5HP</t>
+  </si>
+  <si>
+    <t>Henkestrasse</t>
+  </si>
+  <si>
+    <t>91052</t>
+  </si>
+  <si>
+    <t>Avenue du Général Eisenhower</t>
+  </si>
+  <si>
+    <t>31000</t>
+  </si>
+  <si>
+    <t>Via C. Olivetti</t>
+  </si>
+  <si>
+    <t>20864</t>
+  </si>
+  <si>
+    <t>980 Great West Road</t>
+  </si>
+  <si>
+    <t>TW8 9GS</t>
+  </si>
+  <si>
+    <t>Friedrich-Ebert-Allee</t>
+  </si>
+  <si>
+    <t>53113</t>
+  </si>
+  <si>
+    <t>100 Victoria Embankment</t>
+  </si>
+  <si>
+    <t>EC4Y 0DY</t>
+  </si>
+  <si>
+    <t>16 Boulevard des Italiens</t>
+  </si>
+  <si>
+    <t>75009</t>
+  </si>
+  <si>
+    <t>Königinstrasse</t>
+  </si>
+  <si>
+    <t>80802</t>
+  </si>
+  <si>
+    <t>Petuelring</t>
+  </si>
+  <si>
+    <t>80809</t>
+  </si>
+  <si>
+    <t>Corso Giovanni Agnelli</t>
+  </si>
+  <si>
+    <t>10135</t>
+  </si>
+  <si>
+    <t>Airside Business Park</t>
+  </si>
+  <si>
+    <t>K67</t>
+  </si>
+  <si>
+    <t>Mythenquai</t>
+  </si>
+  <si>
+    <t>8002</t>
+  </si>
+  <si>
+    <t>Austrasse</t>
+  </si>
+  <si>
+    <t>8045</t>
+  </si>
+  <si>
+    <t>17 Boulevard Haussmann</t>
+  </si>
+  <si>
+    <t>Adi-Dassler-Strasse</t>
+  </si>
+  <si>
+    <t>91074</t>
+  </si>
+  <si>
+    <t>22 Avenue Montaigne</t>
+  </si>
+  <si>
+    <t>Boulevard de Grenelle</t>
+  </si>
+  <si>
+    <t>75015</t>
+  </si>
+  <si>
+    <t>Brüsseler Platz</t>
+  </si>
+  <si>
+    <t>45131</t>
+  </si>
+  <si>
+    <t>Aegonplein</t>
+  </si>
+  <si>
+    <t>2591 TV</t>
+  </si>
+  <si>
+    <t>Boulevard des Italiens</t>
+  </si>
+  <si>
+    <t>Glencore Headquarters</t>
+  </si>
+  <si>
+    <t>Aleksanterinkatu</t>
+  </si>
+  <si>
+    <t>Boulevard Haussmann</t>
+  </si>
+  <si>
+    <t>Havenlaan</t>
+  </si>
+  <si>
+    <t>1080</t>
+  </si>
+  <si>
+    <t>Avenue de la Liberté</t>
+  </si>
+  <si>
+    <t>1930</t>
+  </si>
+  <si>
+    <t>Rue d’Anjou</t>
+  </si>
+  <si>
+    <t>Europalaan</t>
+  </si>
+  <si>
+    <t>6161</t>
+  </si>
+  <si>
+    <t>Prinses Beatrixlaan</t>
+  </si>
+  <si>
+    <t>2595 AK</t>
+  </si>
+  <si>
+    <t>Boulevard de la Madeleine</t>
+  </si>
+  <si>
+    <t>Avenue Matignon</t>
+  </si>
+  <si>
+    <t>92000</t>
+  </si>
+  <si>
+    <t>33 Holborn</t>
+  </si>
+  <si>
+    <t>EC1N 2HT</t>
+  </si>
+  <si>
+    <t>EC4Y 0HQ</t>
+  </si>
+  <si>
+    <t>Building 5, The Heights</t>
+  </si>
+  <si>
+    <t>KT13 0NY</t>
+  </si>
+  <si>
+    <t>Kaiser‑Wilhelm‑Allee</t>
+  </si>
+  <si>
+    <t>51373</t>
+  </si>
+  <si>
+    <t>164 40</t>
+  </si>
+  <si>
+    <t>Havneholmen</t>
+  </si>
+  <si>
+    <t>1561</t>
+  </si>
+  <si>
+    <t>Klarabergsviadukten</t>
+  </si>
+  <si>
+    <t>111 64</t>
+  </si>
+  <si>
+    <t>Shire Park</t>
+  </si>
+  <si>
+    <t>AL7 1TW</t>
+  </si>
+  <si>
+    <t>25 Gresham Street</t>
+  </si>
+  <si>
+    <t>EC2V 7HN</t>
+  </si>
+  <si>
+    <t>Viale Regina Margherita</t>
+  </si>
+  <si>
+    <t>00198</t>
+  </si>
+  <si>
+    <t>Piazza San Carlo</t>
+  </si>
+  <si>
+    <t>10121</t>
+  </si>
+  <si>
+    <t>Avenue Jean Jaurès</t>
+  </si>
+  <si>
+    <t>Sandvikens Industripark</t>
+  </si>
+  <si>
+    <t>811 81</t>
+  </si>
+  <si>
+    <t>Waterside House</t>
+  </si>
+  <si>
+    <t>W2 1NW</t>
+  </si>
+  <si>
+    <t>Huizermaatweg</t>
+  </si>
+  <si>
+    <t>1276 LJ</t>
+  </si>
+  <si>
+    <t>Carl‑Bosch‑Strasse</t>
+  </si>
+  <si>
+    <t>40 Rue de Sèvres</t>
+  </si>
+  <si>
+    <t>75007</t>
+  </si>
+  <si>
+    <t>Gifhorner Strasse</t>
+  </si>
+  <si>
+    <t>38112</t>
+  </si>
+  <si>
+    <t>Calle Príncipe de Vergara</t>
+  </si>
+  <si>
+    <t>28002</t>
+  </si>
+  <si>
+    <t>tř. Václava Klementa</t>
+  </si>
+  <si>
+    <t>293 01</t>
+  </si>
+  <si>
+    <t>Viale Europa</t>
+  </si>
+  <si>
+    <t>00144</t>
+  </si>
+  <si>
+    <t>Avenida 24 de Julho</t>
+  </si>
+  <si>
+    <t>1200‑161</t>
+  </si>
+  <si>
+    <t>Avenue Hoche</t>
+  </si>
+  <si>
+    <t>Rue Albert Dhalenne</t>
+  </si>
+  <si>
+    <t>93400</t>
+  </si>
+  <si>
+    <t>Avenida da Liberdade</t>
+  </si>
+  <si>
+    <t>1250‑141</t>
+  </si>
+  <si>
+    <t>Hornsgatan</t>
+  </si>
+  <si>
+    <t>415 50</t>
+  </si>
+  <si>
+    <t>1 Braham Street</t>
+  </si>
+  <si>
+    <t>E1 8EE</t>
+  </si>
+  <si>
+    <t>Victoria Street</t>
+  </si>
+  <si>
+    <t>SW1H 0NF</t>
+  </si>
+  <si>
+    <t>Kanavaranta</t>
+  </si>
+  <si>
+    <t>00160</t>
+  </si>
+  <si>
+    <t>Baggot Street Lower</t>
+  </si>
+  <si>
+    <t>D02 HW68</t>
+  </si>
+  <si>
+    <t>Stonemasons Way</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>Piazza Duca degli Abruzzi</t>
+  </si>
+  <si>
+    <t>34132</t>
+  </si>
+  <si>
+    <t>Piazza Santa Barbara</t>
+  </si>
+  <si>
+    <t>20097</t>
+  </si>
+  <si>
+    <t>Kühne + Nagel Strasse</t>
+  </si>
+  <si>
+    <t>8834</t>
+  </si>
+  <si>
+    <t>Frankfurter Strasse</t>
+  </si>
+  <si>
+    <t>64293</t>
+  </si>
+  <si>
+    <t>Evenemangsgatan</t>
+  </si>
+  <si>
+    <t>169 79</t>
+  </si>
+  <si>
+    <t>Einsteinring</t>
+  </si>
+  <si>
+    <t>85609</t>
+  </si>
+  <si>
+    <t>Dorset Rise</t>
+  </si>
+  <si>
+    <t>EC4Y 8EN</t>
+  </si>
+  <si>
+    <t>Marxergasse</t>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>Messeallee</t>
+  </si>
+  <si>
+    <t>Windsor Street</t>
+  </si>
+  <si>
+    <t>B7 4NF</t>
+  </si>
+  <si>
+    <t>Boulevard de la Mission Marchand</t>
+  </si>
+  <si>
+    <t>Arendalsvägen</t>
+  </si>
+  <si>
+    <t>418 78</t>
+  </si>
+  <si>
+    <t>Drottninggatan</t>
+  </si>
+  <si>
+    <t>111 51</t>
+  </si>
+  <si>
+    <t>Rue du Parc</t>
+  </si>
+  <si>
+    <t>92200</t>
+  </si>
+  <si>
+    <t>Bechtle Platz</t>
+  </si>
+  <si>
+    <t>74172</t>
+  </si>
+  <si>
+    <t>Maxfeldstrasse</t>
+  </si>
+  <si>
+    <t>90409</t>
+  </si>
+  <si>
+    <t>Snarøyveien</t>
+  </si>
+  <si>
+    <t>1360</t>
+  </si>
+  <si>
+    <t>Ratavartijankatu</t>
+  </si>
+  <si>
+    <t>00520</t>
+  </si>
+  <si>
+    <t>Aeschengraben</t>
+  </si>
+  <si>
+    <t>4051</t>
+  </si>
+  <si>
+    <t>Veurse Achterweg</t>
+  </si>
+  <si>
+    <t>2264 SG</t>
+  </si>
+  <si>
+    <t>Karenslyst Allé</t>
+  </si>
+  <si>
+    <t>0277</t>
+  </si>
+  <si>
+    <t>Schweigaards gate</t>
+  </si>
+  <si>
+    <t>0191</t>
+  </si>
+  <si>
+    <t>Rheinmetall Allee</t>
+  </si>
+  <si>
+    <t>40476</t>
   </si>
 </sst>
 </file>
@@ -2157,7 +4173,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2165,11 +4181,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2186,6 +4211,14 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2466,7 +4499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J376"/>
+  <dimension ref="A1:DV881"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" style="1" customWidth="1"/>
@@ -2476,7 +4509,7 @@
     <col min="5" max="5" width="8.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="30.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.109375" style="1" customWidth="1"/>
   </cols>
@@ -8660,7 +10693,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>577</v>
       </c>
@@ -8677,7 +10710,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>583</v>
       </c>
@@ -8694,7 +10727,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>591</v>
       </c>
@@ -8711,7 +10744,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>594</v>
       </c>
@@ -8728,7 +10761,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>380</v>
       </c>
@@ -8745,7 +10778,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>600</v>
       </c>
@@ -8762,7 +10795,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:126" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>606</v>
       </c>
@@ -8779,21 +10812,7212 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A376" s="1" t="s">
+    <row r="376" spans="1:126" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A376" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B376">
+      <c r="B376" s="9">
         <v>754</v>
       </c>
-      <c r="C376" s="6" t="s">
+      <c r="C376" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="D376" t="s">
+      <c r="D376" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="H376" s="1">
+      <c r="E376" s="8"/>
+      <c r="F376" s="8"/>
+      <c r="G376" s="8"/>
+      <c r="H376" s="8">
         <v>176</v>
+      </c>
+      <c r="I376" s="8"/>
+      <c r="J376" s="8"/>
+      <c r="K376" s="9"/>
+      <c r="L376" s="9"/>
+      <c r="M376" s="9"/>
+      <c r="N376" s="9"/>
+      <c r="O376" s="9"/>
+      <c r="P376" s="9"/>
+      <c r="Q376" s="9"/>
+      <c r="R376" s="9"/>
+      <c r="S376" s="9"/>
+      <c r="T376" s="9"/>
+      <c r="U376" s="9"/>
+      <c r="V376" s="9"/>
+      <c r="W376" s="9"/>
+      <c r="X376" s="9"/>
+      <c r="Y376" s="9"/>
+      <c r="Z376" s="9"/>
+      <c r="AA376" s="9"/>
+      <c r="AB376" s="9"/>
+      <c r="AC376" s="9"/>
+      <c r="AD376" s="9"/>
+      <c r="AE376" s="9"/>
+      <c r="AF376" s="9"/>
+      <c r="AG376" s="9"/>
+      <c r="AH376" s="9"/>
+      <c r="AI376" s="9"/>
+      <c r="AJ376" s="9"/>
+      <c r="AK376" s="9"/>
+      <c r="AL376" s="9"/>
+      <c r="AM376" s="9"/>
+      <c r="AN376" s="9"/>
+      <c r="AO376" s="9"/>
+      <c r="AP376" s="9"/>
+      <c r="AQ376" s="9"/>
+      <c r="AR376" s="9"/>
+      <c r="AS376" s="9"/>
+      <c r="AT376" s="9"/>
+      <c r="AU376" s="9"/>
+      <c r="AV376" s="9"/>
+      <c r="AW376" s="9"/>
+      <c r="AX376" s="9"/>
+      <c r="AY376" s="9"/>
+      <c r="AZ376" s="9"/>
+      <c r="BA376" s="9"/>
+      <c r="BB376" s="9"/>
+      <c r="BC376" s="9"/>
+      <c r="BD376" s="9"/>
+      <c r="BE376" s="9"/>
+      <c r="BF376" s="9"/>
+      <c r="BG376" s="9"/>
+      <c r="BH376" s="9"/>
+      <c r="BI376" s="9"/>
+      <c r="BJ376" s="9"/>
+      <c r="BK376" s="9"/>
+      <c r="BL376" s="9"/>
+      <c r="BM376" s="9"/>
+      <c r="BN376" s="9"/>
+      <c r="BO376" s="9"/>
+      <c r="BP376" s="9"/>
+      <c r="BQ376" s="9"/>
+      <c r="BR376" s="9"/>
+      <c r="BS376" s="9"/>
+      <c r="BT376" s="9"/>
+      <c r="BU376" s="9"/>
+      <c r="BV376" s="9"/>
+      <c r="BW376" s="9"/>
+      <c r="BX376" s="9"/>
+      <c r="BY376" s="9"/>
+      <c r="BZ376" s="9"/>
+      <c r="CA376" s="9"/>
+      <c r="CB376" s="9"/>
+      <c r="CC376" s="9"/>
+      <c r="CD376" s="9"/>
+      <c r="CE376" s="9"/>
+      <c r="CF376" s="9"/>
+      <c r="CG376" s="9"/>
+      <c r="CH376" s="9"/>
+      <c r="CI376" s="9"/>
+      <c r="CJ376" s="9"/>
+      <c r="CK376" s="9"/>
+      <c r="CL376" s="9"/>
+      <c r="CM376" s="9"/>
+      <c r="CN376" s="9"/>
+      <c r="CO376" s="9"/>
+      <c r="CP376" s="9"/>
+      <c r="CQ376" s="9"/>
+      <c r="CR376" s="9"/>
+      <c r="CS376" s="9"/>
+      <c r="CT376" s="9"/>
+      <c r="CU376" s="9"/>
+      <c r="CV376" s="9"/>
+      <c r="CW376" s="9"/>
+      <c r="CX376" s="9"/>
+      <c r="CY376" s="9"/>
+      <c r="CZ376" s="9"/>
+      <c r="DA376" s="9"/>
+      <c r="DB376" s="9"/>
+      <c r="DC376" s="9"/>
+      <c r="DD376" s="9"/>
+      <c r="DE376" s="9"/>
+      <c r="DF376" s="9"/>
+      <c r="DG376" s="9"/>
+      <c r="DH376" s="9"/>
+      <c r="DI376" s="9"/>
+      <c r="DJ376" s="9"/>
+      <c r="DK376" s="9"/>
+      <c r="DL376" s="9"/>
+      <c r="DM376" s="9"/>
+      <c r="DN376" s="9"/>
+      <c r="DO376" s="9"/>
+      <c r="DP376" s="9"/>
+      <c r="DQ376" s="9"/>
+      <c r="DR376" s="9"/>
+      <c r="DS376" s="9"/>
+      <c r="DT376" s="9"/>
+      <c r="DU376" s="9"/>
+      <c r="DV376" s="9"/>
+    </row>
+    <row r="377" spans="1:126" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B377">
+        <v>201</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H377" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="378" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A378" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B378">
+        <v>5</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H378" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="379" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A379" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B379">
+        <v>12</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="H379" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="380" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A380" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B380">
+        <v>12</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="H380" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="381" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A381" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B381">
+        <v>6</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="H381" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="382" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A382" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B382">
+        <v>14</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="H382" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="383" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A383" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B383">
+        <v>12</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="H383" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="384" spans="1:126" x14ac:dyDescent="0.3">
+      <c r="A384" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B384">
+        <v>20</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="H384" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A385" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B385">
+        <v>31</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H385" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A386" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B386">
+        <v>26</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="H386" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A387" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B387">
+        <v>246</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="H387" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A388" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B388">
+        <v>9</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H388" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A389" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B389">
+        <v>14</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="H389" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A390" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B390">
+        <v>45</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="H390" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A391" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B391">
+        <v>40</v>
+      </c>
+      <c r="C391" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="H391" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A392" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B392">
+        <v>45</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="H392" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A393" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B393" s="11">
+        <v>46082</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="H393" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A394" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B394" s="11">
+        <v>46240</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="H394" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A395" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B395" s="11">
+        <v>121</v>
+      </c>
+      <c r="C395" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="H395" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B396" s="11">
+        <v>25</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="H396" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A397" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B397" s="11">
+        <v>105</v>
+      </c>
+      <c r="C397" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="H397" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A398" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B398" s="11">
+        <v>14</v>
+      </c>
+      <c r="C398" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="H398" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A399" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B399" s="11">
+        <v>1</v>
+      </c>
+      <c r="C399" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="H399" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A400" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B400" s="11">
+        <v>45</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="H400" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A401" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B401" s="11">
+        <v>201</v>
+      </c>
+      <c r="C401" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H401" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A402" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B402" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="H402" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A403" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B403" s="11">
+        <v>2</v>
+      </c>
+      <c r="C403" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="H403" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A404" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B404" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="C404" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H404" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A405" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B405" s="11">
+        <v>8</v>
+      </c>
+      <c r="C405" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="H405" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A406" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B406" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="C406" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="H406" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A407" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B407">
+        <v>6</v>
+      </c>
+      <c r="C407" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H407" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A408" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B408">
+        <v>76</v>
+      </c>
+      <c r="C408" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="H408" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A409" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B409">
+        <v>164</v>
+      </c>
+      <c r="C409" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="H409" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A410" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B410">
+        <v>72</v>
+      </c>
+      <c r="C410" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H410" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A411" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B411">
+        <v>239</v>
+      </c>
+      <c r="C411" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="H411" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A412" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B412">
+        <v>12</v>
+      </c>
+      <c r="C412" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="H412" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A413" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B413">
+        <v>45</v>
+      </c>
+      <c r="C413" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="H413" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A414" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B414">
+        <v>30</v>
+      </c>
+      <c r="C414" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="H414" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A415" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B415">
+        <v>7</v>
+      </c>
+      <c r="C415" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="H415" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A416" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B416">
+        <v>51</v>
+      </c>
+      <c r="C416" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="H416" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A417" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B417">
+        <v>29</v>
+      </c>
+      <c r="C417" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="H417" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A418" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B418">
+        <v>121</v>
+      </c>
+      <c r="C418" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="H418" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A419" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B419">
+        <v>45</v>
+      </c>
+      <c r="C419" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="H419" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A420" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B420">
+        <v>51</v>
+      </c>
+      <c r="C420" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="H420" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B421">
+        <v>48</v>
+      </c>
+      <c r="C421" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="H421" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A422" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B422">
+        <v>77</v>
+      </c>
+      <c r="C422" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="H422" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A423" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B423">
+        <v>201</v>
+      </c>
+      <c r="C423" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H423" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A424" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B424">
+        <v>30</v>
+      </c>
+      <c r="C424" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="H424" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A425" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B425">
+        <v>7</v>
+      </c>
+      <c r="C425" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="H425" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B426">
+        <v>6</v>
+      </c>
+      <c r="C426" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H426" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B427">
+        <v>14</v>
+      </c>
+      <c r="C427" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="H427" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A428" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B428">
+        <v>1989</v>
+      </c>
+      <c r="C428" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="H428" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B429">
+        <v>6</v>
+      </c>
+      <c r="C429" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="H429" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A430" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B430">
+        <v>24</v>
+      </c>
+      <c r="C430" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="H430" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A431" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B431">
+        <v>24</v>
+      </c>
+      <c r="C431" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="H431" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A432" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B432">
+        <v>148</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="H432" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A433" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B433">
+        <v>3</v>
+      </c>
+      <c r="C433" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="H433" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A434" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B434">
+        <v>63</v>
+      </c>
+      <c r="C434" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H434" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A435" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B435">
+        <v>4</v>
+      </c>
+      <c r="C435" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="H435" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A436" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B436">
+        <v>24</v>
+      </c>
+      <c r="C436" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="H436" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A437" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B437">
+        <v>9</v>
+      </c>
+      <c r="C437" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H437" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A438" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B438">
+        <v>45</v>
+      </c>
+      <c r="C438" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="H438" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A439" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="B439">
+        <v>31</v>
+      </c>
+      <c r="C439" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H439" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A440" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B440">
+        <v>2</v>
+      </c>
+      <c r="C440" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="H440" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A441" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B441">
+        <v>48</v>
+      </c>
+      <c r="C441" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="H441" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A442" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B442">
+        <v>5</v>
+      </c>
+      <c r="C442" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="H442" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A443" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B443">
+        <v>15</v>
+      </c>
+      <c r="C443" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="H443" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A444" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B444">
+        <v>68</v>
+      </c>
+      <c r="C444" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="H444" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A445" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B445">
+        <v>3</v>
+      </c>
+      <c r="C445" s="6" t="s">
+        <v>785</v>
+      </c>
+      <c r="H445" s="1">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A446" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B446">
+        <v>63</v>
+      </c>
+      <c r="C446" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H446" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A447" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B447">
+        <v>4</v>
+      </c>
+      <c r="C447" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="H447" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A448" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B448">
+        <v>24</v>
+      </c>
+      <c r="C448" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="H448" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A449" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B449">
+        <v>76</v>
+      </c>
+      <c r="C449" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="H449" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A450" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B450">
+        <v>27</v>
+      </c>
+      <c r="C450" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="H450" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A451" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B451">
+        <v>6</v>
+      </c>
+      <c r="C451" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="H451" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A452" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B452">
+        <v>31</v>
+      </c>
+      <c r="C452" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="H452" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A453" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="B453">
+        <v>12</v>
+      </c>
+      <c r="C453" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="H453" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A454" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B454">
+        <v>109</v>
+      </c>
+      <c r="C454" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="H454" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A455" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B455">
+        <v>15</v>
+      </c>
+      <c r="C455" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="H455" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A456" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B456">
+        <v>76</v>
+      </c>
+      <c r="C456" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="H456" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A457" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B457">
+        <v>45</v>
+      </c>
+      <c r="C457" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="H457" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A458" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B458">
+        <v>4</v>
+      </c>
+      <c r="C458" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="H458" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A459" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B459">
+        <v>29</v>
+      </c>
+      <c r="C459" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="H459" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A460" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B460">
+        <v>12</v>
+      </c>
+      <c r="C460" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="H460" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A461" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B461">
+        <v>8</v>
+      </c>
+      <c r="C461" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="H461" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A462" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B462">
+        <v>34</v>
+      </c>
+      <c r="C462" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="H462" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A463" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B463">
+        <v>47</v>
+      </c>
+      <c r="C463" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="H463" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A464" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B464">
+        <v>22</v>
+      </c>
+      <c r="C464" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="H464" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A465" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B465">
+        <v>3</v>
+      </c>
+      <c r="C465" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="H465" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A466" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B466">
+        <v>65</v>
+      </c>
+      <c r="C466" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="H466" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A467" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B467">
+        <v>164</v>
+      </c>
+      <c r="C467" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="H467" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A468" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B468">
+        <v>18</v>
+      </c>
+      <c r="C468" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="H468" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A469" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B469">
+        <v>27</v>
+      </c>
+      <c r="C469" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="H469" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A470" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B470">
+        <v>34</v>
+      </c>
+      <c r="C470" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="H470" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A471" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B471">
+        <v>47</v>
+      </c>
+      <c r="C471" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="H471" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A472" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B472">
+        <v>31</v>
+      </c>
+      <c r="C472" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="H472" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A473" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B473">
+        <v>15</v>
+      </c>
+      <c r="C473" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="H473" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A474" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B474">
+        <v>109</v>
+      </c>
+      <c r="C474" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="H474" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A475" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B475">
+        <v>76</v>
+      </c>
+      <c r="C475" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="H475" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A476" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B476">
+        <v>3</v>
+      </c>
+      <c r="C476" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="H476" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A477" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B477">
+        <v>63</v>
+      </c>
+      <c r="C477" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="H477" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A478" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B478">
+        <v>1989</v>
+      </c>
+      <c r="C478" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="H478" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A479" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B479">
+        <v>29</v>
+      </c>
+      <c r="C479" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="H479" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A480" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B480">
+        <v>34</v>
+      </c>
+      <c r="C480" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="H480" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A481" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B481">
+        <v>47</v>
+      </c>
+      <c r="C481" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="H481" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A482" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B482">
+        <v>22</v>
+      </c>
+      <c r="C482" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="H482" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A483" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B483">
+        <v>15</v>
+      </c>
+      <c r="C483" s="6" t="s">
+        <v>796</v>
+      </c>
+      <c r="H483" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A484" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B484">
+        <v>109</v>
+      </c>
+      <c r="C484" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="H484" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A485" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B485">
+        <v>76</v>
+      </c>
+      <c r="C485" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="H485" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A486" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B486">
+        <v>11</v>
+      </c>
+      <c r="C486" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="H486" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A487" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B487">
+        <v>14</v>
+      </c>
+      <c r="C487" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="H487" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A488" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B488">
+        <v>51</v>
+      </c>
+      <c r="C488" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="H488" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A489" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B489">
+        <v>5</v>
+      </c>
+      <c r="C489" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="H489" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A490" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B490">
+        <v>10</v>
+      </c>
+      <c r="C490" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="H490" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A491" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B491">
+        <v>71</v>
+      </c>
+      <c r="C491" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H491" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A492" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B492">
+        <v>75</v>
+      </c>
+      <c r="C492" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="H492" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A493" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B493">
+        <v>1</v>
+      </c>
+      <c r="C493" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="H493" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A494" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B494">
+        <v>129</v>
+      </c>
+      <c r="C494" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="H494" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A495" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B495">
+        <v>62</v>
+      </c>
+      <c r="C495" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="H495" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A496" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B496">
+        <v>9</v>
+      </c>
+      <c r="C496" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H496" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A497" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B497">
+        <v>25</v>
+      </c>
+      <c r="C497" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="H497" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A498" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B498">
+        <v>22</v>
+      </c>
+      <c r="C498" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="H498" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A499" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B499">
+        <v>48</v>
+      </c>
+      <c r="C499" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="H499" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A500" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B500">
+        <v>10</v>
+      </c>
+      <c r="C500" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="H500" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A501" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B501">
+        <v>89</v>
+      </c>
+      <c r="C501" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H501" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A502" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B502">
+        <v>208</v>
+      </c>
+      <c r="C502" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="H502" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A503" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B503">
+        <v>12</v>
+      </c>
+      <c r="C503" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="H503" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A504" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B504">
+        <v>18</v>
+      </c>
+      <c r="C504" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="H504" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A505" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B505">
+        <v>14</v>
+      </c>
+      <c r="C505" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="H505" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A506" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B506">
+        <v>73</v>
+      </c>
+      <c r="C506" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H506" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A507" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B507">
+        <v>102</v>
+      </c>
+      <c r="C507" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="H507" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A508" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B508">
+        <v>62</v>
+      </c>
+      <c r="C508" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="H508" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A509" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B509">
+        <v>26</v>
+      </c>
+      <c r="C509" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="H509" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A510" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="B510">
+        <v>18</v>
+      </c>
+      <c r="C510" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="H510" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A511" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B511">
+        <v>201</v>
+      </c>
+      <c r="C511" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H511" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A512" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B512">
+        <v>182</v>
+      </c>
+      <c r="C512" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="H512" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A513" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B513">
+        <v>244</v>
+      </c>
+      <c r="C513" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="H513" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A514" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B514">
+        <v>31</v>
+      </c>
+      <c r="C514" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="H514" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A515" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B515">
+        <v>47</v>
+      </c>
+      <c r="C515" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="H515" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A516" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B516">
+        <v>12</v>
+      </c>
+      <c r="C516" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="H516" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A517" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B517">
+        <v>125</v>
+      </c>
+      <c r="C517" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="H517" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A518" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B518">
+        <v>17</v>
+      </c>
+      <c r="C518" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="H518" s="1">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A519" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B519">
+        <v>29</v>
+      </c>
+      <c r="C519" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="H519" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A520" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B520">
+        <v>45</v>
+      </c>
+      <c r="C520" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="H520" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A521" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="B521">
+        <v>60</v>
+      </c>
+      <c r="C521" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="H521" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A522" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B522">
+        <v>287</v>
+      </c>
+      <c r="C522" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="H522" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A523" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B523">
+        <v>270</v>
+      </c>
+      <c r="C523" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="H523" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A524" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B524">
+        <v>89</v>
+      </c>
+      <c r="C524" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="H524" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A525" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B525">
+        <v>48</v>
+      </c>
+      <c r="C525" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="H525" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A526" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B526">
+        <v>15</v>
+      </c>
+      <c r="C526" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H526" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A527" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B527">
+        <v>33</v>
+      </c>
+      <c r="C527" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="H527" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A528" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B528">
+        <v>92</v>
+      </c>
+      <c r="C528" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="H528" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A529" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B529">
+        <v>16</v>
+      </c>
+      <c r="C529" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="H529" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A530" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B530">
+        <v>6</v>
+      </c>
+      <c r="C530" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H530" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A531" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B531">
+        <v>100</v>
+      </c>
+      <c r="C531" s="6" t="s">
+        <v>881</v>
+      </c>
+      <c r="H531" s="1">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A532" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B532">
+        <v>47</v>
+      </c>
+      <c r="C532" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="H532" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A533" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B533">
+        <v>201</v>
+      </c>
+      <c r="C533" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H533" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A534" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B534">
+        <v>10</v>
+      </c>
+      <c r="C534" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="H534" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A535" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B535">
+        <v>1</v>
+      </c>
+      <c r="C535" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="H535" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A536" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B536">
+        <v>30</v>
+      </c>
+      <c r="C536" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="H536" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A537" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B537">
+        <v>26</v>
+      </c>
+      <c r="C537" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="H537" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A538" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B538">
+        <v>21</v>
+      </c>
+      <c r="C538" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="H538" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A539" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="B539">
+        <v>2</v>
+      </c>
+      <c r="C539" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H539" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A540" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B540">
+        <v>48</v>
+      </c>
+      <c r="C540" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="H540" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A541" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B541">
+        <v>6</v>
+      </c>
+      <c r="C541" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="H541" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A542" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B542">
+        <v>85</v>
+      </c>
+      <c r="C542" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H542" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A543" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B543">
+        <v>51</v>
+      </c>
+      <c r="C543" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="H543" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A544" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B544">
+        <v>10</v>
+      </c>
+      <c r="C544" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="H544" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A545" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B545">
+        <v>15</v>
+      </c>
+      <c r="C545" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="H545" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A546" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B546">
+        <v>284</v>
+      </c>
+      <c r="C546" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="H546" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A547" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B547">
+        <v>5</v>
+      </c>
+      <c r="C547" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="H547" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A548" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B548">
+        <v>546</v>
+      </c>
+      <c r="C548" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="H548" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A549" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B549">
+        <v>55</v>
+      </c>
+      <c r="C549" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="H549" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A550" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B550">
+        <v>29</v>
+      </c>
+      <c r="C550" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="H550" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A551" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B551">
+        <v>46</v>
+      </c>
+      <c r="C551" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H551" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A552" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B552">
+        <v>234</v>
+      </c>
+      <c r="C552" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="H552" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A553" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B553">
+        <v>20</v>
+      </c>
+      <c r="C553" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="H553" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A554" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B554">
+        <v>68</v>
+      </c>
+      <c r="C554" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="H554" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A555" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B555">
+        <v>3</v>
+      </c>
+      <c r="C555" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="H555" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A556" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B556">
+        <v>8</v>
+      </c>
+      <c r="C556" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="H556" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A557" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B557">
+        <v>270</v>
+      </c>
+      <c r="C557" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="H557" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A558" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B558">
+        <v>1</v>
+      </c>
+      <c r="C558" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="H558" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A559" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B559">
+        <v>2</v>
+      </c>
+      <c r="C559" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="H559" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A560" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B560">
+        <v>12</v>
+      </c>
+      <c r="C560" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="H560" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A561" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B561">
+        <v>7</v>
+      </c>
+      <c r="C561" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="H561" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A562" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B562">
+        <v>47</v>
+      </c>
+      <c r="C562" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="H562" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A563" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B563">
+        <v>1</v>
+      </c>
+      <c r="C563" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="H563" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A564" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B564">
+        <v>9</v>
+      </c>
+      <c r="C564" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="H564" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A565" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B565">
+        <v>15</v>
+      </c>
+      <c r="C565" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="H565" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A566" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B566">
+        <v>1</v>
+      </c>
+      <c r="C566" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="H566" s="1">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A567" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B567">
+        <v>33</v>
+      </c>
+      <c r="C567" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="H567" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A568" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B568">
+        <v>65</v>
+      </c>
+      <c r="C568" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="H568" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A569" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B569">
+        <v>82</v>
+      </c>
+      <c r="C569" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="H569" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A570" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B570">
+        <v>224</v>
+      </c>
+      <c r="C570" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="H570" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A571" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B571">
+        <v>6</v>
+      </c>
+      <c r="C571" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="H571" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A572" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B572">
+        <v>4</v>
+      </c>
+      <c r="C572" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="H572" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A573" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B573">
+        <v>38</v>
+      </c>
+      <c r="C573" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="H573" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A574" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B574">
+        <v>1</v>
+      </c>
+      <c r="C574" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H574" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A575" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B575">
+        <v>67</v>
+      </c>
+      <c r="C575" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="H575" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A576" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B576">
+        <v>99</v>
+      </c>
+      <c r="C576" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="H576" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A577" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B577">
+        <v>35</v>
+      </c>
+      <c r="C577" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="H577" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A578" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B578">
+        <v>30</v>
+      </c>
+      <c r="C578" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="H578" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A579" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B579">
+        <v>12</v>
+      </c>
+      <c r="C579" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="H579" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A580" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B580">
+        <v>5</v>
+      </c>
+      <c r="C580" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="H580" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A581" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="B581">
+        <v>34</v>
+      </c>
+      <c r="C581" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="H581" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A582" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B582">
+        <v>1</v>
+      </c>
+      <c r="C582" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="H582" s="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A583" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B583">
+        <v>9</v>
+      </c>
+      <c r="C583" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H583" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A584" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B584">
+        <v>2</v>
+      </c>
+      <c r="C584" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="H584" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A585" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B585">
+        <v>242</v>
+      </c>
+      <c r="C585" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="H585" s="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B586">
+        <v>3</v>
+      </c>
+      <c r="C586" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="H586" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A587" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="B587">
+        <v>4</v>
+      </c>
+      <c r="C587" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="H587" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A588" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B588">
+        <v>113</v>
+      </c>
+      <c r="C588" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="H588" s="1">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A589" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="B589">
+        <v>224</v>
+      </c>
+      <c r="C589" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="H589" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A590" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B590">
+        <v>15</v>
+      </c>
+      <c r="C590" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="H590" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A591" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B591">
+        <v>35</v>
+      </c>
+      <c r="C591" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="H591" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A592" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B592">
+        <v>1</v>
+      </c>
+      <c r="C592" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="H592" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A593" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B593">
+        <v>10</v>
+      </c>
+      <c r="C593" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="H593" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A594" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B594">
+        <v>6</v>
+      </c>
+      <c r="C594" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="H594" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A595" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B595">
+        <v>31</v>
+      </c>
+      <c r="C595" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="H595" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A596" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B596">
+        <v>50</v>
+      </c>
+      <c r="C596" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="H596" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A597" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B597">
+        <v>51</v>
+      </c>
+      <c r="C597" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="H597" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A598" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B598">
+        <v>144</v>
+      </c>
+      <c r="C598" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="H598" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A599" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B599">
+        <v>201</v>
+      </c>
+      <c r="C599" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H599" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A600" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="B600">
+        <v>2</v>
+      </c>
+      <c r="C600" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="H600" s="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A601" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B601">
+        <v>11</v>
+      </c>
+      <c r="C601" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="H601" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A602" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B602">
+        <v>63</v>
+      </c>
+      <c r="C602" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="H602" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A603" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B603">
+        <v>2</v>
+      </c>
+      <c r="C603" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="H603" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A604" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B604">
+        <v>2</v>
+      </c>
+      <c r="C604" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="H604" s="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A605" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B605">
+        <v>44</v>
+      </c>
+      <c r="C605" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="H605" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A606" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B606">
+        <v>26</v>
+      </c>
+      <c r="C606" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="H606" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A607" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B607">
+        <v>1</v>
+      </c>
+      <c r="C607" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="H607" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A608" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B608">
+        <v>4</v>
+      </c>
+      <c r="C608" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="H608" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A609" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B609">
+        <v>18</v>
+      </c>
+      <c r="C609" s="6" t="s">
+        <v>974</v>
+      </c>
+      <c r="H609" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A610" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B610">
+        <v>10</v>
+      </c>
+      <c r="C610" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="H610" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A611" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B611">
+        <v>20</v>
+      </c>
+      <c r="C611" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="H611" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A612" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B612">
+        <v>15</v>
+      </c>
+      <c r="C612" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="H612" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A613" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B613">
+        <v>42</v>
+      </c>
+      <c r="C613" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="H613" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A614" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B614">
+        <v>38</v>
+      </c>
+      <c r="C614" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="H614" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A615" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B615">
+        <v>55</v>
+      </c>
+      <c r="C615" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="H615" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A616" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B616">
+        <v>29</v>
+      </c>
+      <c r="C616" s="6" t="s">
+        <v>979</v>
+      </c>
+      <c r="H616" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A617" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B617">
+        <v>3</v>
+      </c>
+      <c r="C617" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="H617" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A618" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B618">
+        <v>3</v>
+      </c>
+      <c r="C618" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="H618" s="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A619" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B619">
+        <v>1</v>
+      </c>
+      <c r="C619" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="H619" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A620" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B620">
+        <v>112</v>
+      </c>
+      <c r="C620" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="H620" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A621" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B621">
+        <v>98</v>
+      </c>
+      <c r="C621" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="H621" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A622" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B622">
+        <v>21</v>
+      </c>
+      <c r="C622" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="H622" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A623" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B623">
+        <v>62</v>
+      </c>
+      <c r="C623" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="H623" s="1">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A624" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B624">
+        <v>22</v>
+      </c>
+      <c r="C624" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="H624" s="1">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A625" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B625">
+        <v>201</v>
+      </c>
+      <c r="C625" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H625" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A626" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B626">
+        <v>9</v>
+      </c>
+      <c r="C626" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="H626" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A627" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B627">
+        <v>45</v>
+      </c>
+      <c r="C627" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="H627" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A628" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="B628">
+        <v>1</v>
+      </c>
+      <c r="C628" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="H628" s="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A629" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B629">
+        <v>2</v>
+      </c>
+      <c r="C629" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="H629" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A630" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B630">
+        <v>1</v>
+      </c>
+      <c r="C630" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="H630" s="1">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A631" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B631">
+        <v>12</v>
+      </c>
+      <c r="C631" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="H631" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A632" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B632">
+        <v>48</v>
+      </c>
+      <c r="C632" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="H632" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A633" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B633">
+        <v>5</v>
+      </c>
+      <c r="C633" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H633" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A634" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B634">
+        <v>178</v>
+      </c>
+      <c r="C634" s="6" t="s">
+        <v>828</v>
+      </c>
+      <c r="H634" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A635" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B635">
+        <v>1</v>
+      </c>
+      <c r="C635" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H635" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A636" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B636">
+        <v>51</v>
+      </c>
+      <c r="C636" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H636" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A637" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B637">
+        <v>12</v>
+      </c>
+      <c r="C637" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H637" s="1">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A638" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B638">
+        <v>9</v>
+      </c>
+      <c r="C638" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="H638" s="1">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A639" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B639">
+        <v>2</v>
+      </c>
+      <c r="C639" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="H639" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A640" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B640">
+        <v>3</v>
+      </c>
+      <c r="C640" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H640" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A641" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B641">
+        <v>20</v>
+      </c>
+      <c r="C641" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="H641" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A642" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B642">
+        <v>1</v>
+      </c>
+      <c r="C642" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H642" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A643" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B643">
+        <v>120</v>
+      </c>
+      <c r="C643" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H643" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A644" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B644">
+        <v>10</v>
+      </c>
+      <c r="C644" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H644" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A645" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B645">
+        <v>116</v>
+      </c>
+      <c r="C645" s="6" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H645" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A646" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B646">
+        <v>9</v>
+      </c>
+      <c r="C646" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="H646" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A647" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B647">
+        <v>1</v>
+      </c>
+      <c r="C647" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H647" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A648" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B648">
+        <v>266</v>
+      </c>
+      <c r="C648" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H648" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A649" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B649">
+        <v>244</v>
+      </c>
+      <c r="C649" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H649" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A650" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B650">
+        <v>4</v>
+      </c>
+      <c r="C650" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H650" s="1">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A651" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B651">
+        <v>45</v>
+      </c>
+      <c r="C651" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H651" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A652" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B652">
+        <v>29</v>
+      </c>
+      <c r="C652" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="H652" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="653" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A653" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B653">
+        <v>12</v>
+      </c>
+      <c r="C653" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="H653" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A654" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B654">
+        <v>45</v>
+      </c>
+      <c r="C654" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H654" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="655" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A655" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B655">
+        <v>4</v>
+      </c>
+      <c r="C655" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="H655" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A656" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B656">
+        <v>5</v>
+      </c>
+      <c r="C656" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H656" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A657" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B657">
+        <v>220</v>
+      </c>
+      <c r="C657" s="6" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H657" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A658" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B658">
+        <v>18</v>
+      </c>
+      <c r="C658" s="6" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H658" s="1">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A659" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B659">
+        <v>231</v>
+      </c>
+      <c r="C659" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H659" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A660" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B660">
+        <v>14</v>
+      </c>
+      <c r="C660" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H660" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A661" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B661">
+        <v>113</v>
+      </c>
+      <c r="C661" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="H661" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A662" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B662">
+        <v>136</v>
+      </c>
+      <c r="C662" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H662" s="1">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A663" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B663">
+        <v>18</v>
+      </c>
+      <c r="C663" s="6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H663" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A664" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B664">
+        <v>12</v>
+      </c>
+      <c r="C664" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="H664" s="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A665" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B665">
+        <v>20</v>
+      </c>
+      <c r="C665" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H665" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A666" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B666">
+        <v>14</v>
+      </c>
+      <c r="C666" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H666" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A667" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B667">
+        <v>2</v>
+      </c>
+      <c r="C667" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H667" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A668" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B668">
+        <v>45</v>
+      </c>
+      <c r="C668" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H668" s="1">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A669" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B669">
+        <v>4</v>
+      </c>
+      <c r="C669" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H669" s="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A670" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B670">
+        <v>289</v>
+      </c>
+      <c r="C670" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H670" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A671" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B671">
+        <v>215</v>
+      </c>
+      <c r="C671" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H671" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A672" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B672">
+        <v>14</v>
+      </c>
+      <c r="C672" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H672" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A673" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B673">
+        <v>89</v>
+      </c>
+      <c r="C673" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H673" s="1">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A674" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B674">
+        <v>44</v>
+      </c>
+      <c r="C674" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H674" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A675" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B675">
+        <v>23</v>
+      </c>
+      <c r="C675" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="H675" s="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A676" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B676">
+        <v>1</v>
+      </c>
+      <c r="C676" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H676" s="1">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A677" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B677">
+        <v>12</v>
+      </c>
+      <c r="C677" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H677" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A678" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B678">
+        <v>49</v>
+      </c>
+      <c r="C678" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H678" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A679" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B679">
+        <v>2</v>
+      </c>
+      <c r="C679" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="H679" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A680" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B680">
+        <v>29</v>
+      </c>
+      <c r="C680" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H680" s="1">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A681" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B681">
+        <v>18</v>
+      </c>
+      <c r="C681" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H681" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A682" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B682">
+        <v>269</v>
+      </c>
+      <c r="C682" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H682" s="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A683" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B683">
+        <v>45</v>
+      </c>
+      <c r="C683" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="H683" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A684" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B684">
+        <v>13</v>
+      </c>
+      <c r="C684" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H684" s="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A685" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B685">
+        <v>2</v>
+      </c>
+      <c r="C685" s="6" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H685" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A686" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B686">
+        <v>18</v>
+      </c>
+      <c r="C686" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H686" s="1">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A687" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B687">
+        <v>6</v>
+      </c>
+      <c r="C687" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="H687" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A688" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B688">
+        <v>21</v>
+      </c>
+      <c r="C688" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H688" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A689" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B689">
+        <v>14</v>
+      </c>
+      <c r="C689" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H689" s="1">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A690" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B690">
+        <v>239</v>
+      </c>
+      <c r="C690" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H690" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A691" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B691">
+        <v>7</v>
+      </c>
+      <c r="C691" s="6" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H691" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A692" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B692">
+        <v>75</v>
+      </c>
+      <c r="C692" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="H692" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A693" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B693">
+        <v>6</v>
+      </c>
+      <c r="C693" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="H693" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A694" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B694">
+        <v>46</v>
+      </c>
+      <c r="C694" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H694" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A695" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B695">
+        <v>169</v>
+      </c>
+      <c r="C695" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H695" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A696" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B696">
+        <v>29</v>
+      </c>
+      <c r="C696" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="H696" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A697" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B697">
+        <v>4</v>
+      </c>
+      <c r="C697" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="H697" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A698" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B698">
+        <v>71</v>
+      </c>
+      <c r="C698" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H698" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A699" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B699">
+        <v>5</v>
+      </c>
+      <c r="C699" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H699" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="700" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A700" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B700">
+        <v>6</v>
+      </c>
+      <c r="C700" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="H700" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A701" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B701">
+        <v>7</v>
+      </c>
+      <c r="C701" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="H701" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A702" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B702">
+        <v>201</v>
+      </c>
+      <c r="C702" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="H702" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="703" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A703" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B703">
+        <v>246</v>
+      </c>
+      <c r="C703" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="H703" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A704" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B704">
+        <v>71</v>
+      </c>
+      <c r="C704" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H704" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="705" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A705" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B705">
+        <v>5</v>
+      </c>
+      <c r="C705" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="H705" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="706" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A706" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B706">
+        <v>1</v>
+      </c>
+      <c r="C706" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H706" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="707" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A707" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B707">
+        <v>2</v>
+      </c>
+      <c r="C707" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H707" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="708" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A708" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B708">
+        <v>4</v>
+      </c>
+      <c r="C708" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H708" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A709" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B709">
+        <v>12</v>
+      </c>
+      <c r="C709" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H709" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A710" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B710">
+        <v>29</v>
+      </c>
+      <c r="C710" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H710" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A711" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B711">
+        <v>85</v>
+      </c>
+      <c r="C711" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="H711" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A712" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B712">
+        <v>26</v>
+      </c>
+      <c r="C712" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="H712" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A713" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B713">
+        <v>15</v>
+      </c>
+      <c r="C713" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H713" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A714" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B714">
+        <v>6</v>
+      </c>
+      <c r="C714" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="H714" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A715" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B715">
+        <v>6</v>
+      </c>
+      <c r="C715" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="H715" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A716" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B716">
+        <v>4</v>
+      </c>
+      <c r="C716" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="H716" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A717" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B717">
+        <v>31</v>
+      </c>
+      <c r="C717" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="H717" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A718" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B718">
+        <v>3</v>
+      </c>
+      <c r="C718" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H718" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A719" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B719">
+        <v>71</v>
+      </c>
+      <c r="C719" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="H719" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A720" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B720">
+        <v>90</v>
+      </c>
+      <c r="C720" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H720" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="721" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A721" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B721">
+        <v>3</v>
+      </c>
+      <c r="C721" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="H721" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A722" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B722">
+        <v>2</v>
+      </c>
+      <c r="C722" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H722" s="1">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A723" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B723">
+        <v>1</v>
+      </c>
+      <c r="C723" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H723" s="1">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A724" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B724">
+        <v>16</v>
+      </c>
+      <c r="C724" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H724" s="1">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A725" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B725">
+        <v>1</v>
+      </c>
+      <c r="C725" s="6" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H725" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="726" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A726" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B726">
+        <v>3</v>
+      </c>
+      <c r="C726" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H726" s="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="727" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A727" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B727">
+        <v>21</v>
+      </c>
+      <c r="C727" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H727" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="728" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A728" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B728">
+        <v>10</v>
+      </c>
+      <c r="C728" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H728" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="729" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A729" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B729">
+        <v>597</v>
+      </c>
+      <c r="C729" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H729" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A730" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B730">
+        <v>19</v>
+      </c>
+      <c r="C730" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H730" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="731" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A731" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B731">
+        <v>106</v>
+      </c>
+      <c r="C731" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H731" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="732" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A732" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B732">
+        <v>7</v>
+      </c>
+      <c r="C732" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H732" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="733" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A733" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B733">
+        <v>1</v>
+      </c>
+      <c r="C733" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H733" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A734" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B734">
+        <v>16</v>
+      </c>
+      <c r="C734" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H734" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A735" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B735">
+        <v>46</v>
+      </c>
+      <c r="C735" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H735" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A736" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B736">
+        <v>650</v>
+      </c>
+      <c r="C736" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H736" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="737" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A737" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B737">
+        <v>11</v>
+      </c>
+      <c r="C737" s="6" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H737" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="738" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A738" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B738">
+        <v>74</v>
+      </c>
+      <c r="C738" s="6" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H738" s="1">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="739" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A739" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B739">
+        <v>28</v>
+      </c>
+      <c r="C739" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H739" s="1">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A740" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B740">
+        <v>44</v>
+      </c>
+      <c r="C740" s="6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H740" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A741" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B741">
+        <v>35</v>
+      </c>
+      <c r="C741" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H741" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A742" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B742">
+        <v>190</v>
+      </c>
+      <c r="C742" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H742" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A743" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B743">
+        <v>42</v>
+      </c>
+      <c r="C743" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H743" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A744" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B744">
+        <v>6501</v>
+      </c>
+      <c r="C744" s="6" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H744" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A745" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B745">
+        <v>110</v>
+      </c>
+      <c r="C745" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H745" s="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A746" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B746">
+        <v>2</v>
+      </c>
+      <c r="C746" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H746" s="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="747" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A747" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B747">
+        <v>5</v>
+      </c>
+      <c r="C747" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H747" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="748" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A748" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B748">
+        <v>25</v>
+      </c>
+      <c r="C748" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H748" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="749" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A749" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B749">
+        <v>11</v>
+      </c>
+      <c r="C749" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H749" s="1">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A750" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B750">
+        <v>14</v>
+      </c>
+      <c r="C750" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H750" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="751" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A751" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B751">
+        <v>5</v>
+      </c>
+      <c r="C751" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H751" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="752" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A752" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B752">
+        <v>2</v>
+      </c>
+      <c r="C752" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H752" s="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A753" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B753">
+        <v>55</v>
+      </c>
+      <c r="C753" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H753" s="1">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A754" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B754">
+        <v>52</v>
+      </c>
+      <c r="C754" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H754" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A755" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B755">
+        <v>39</v>
+      </c>
+      <c r="C755" s="6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H755" s="1">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A756" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B756">
+        <v>45</v>
+      </c>
+      <c r="C756" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H756" s="1">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A757" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B757">
+        <v>11</v>
+      </c>
+      <c r="C757" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H757" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A758" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B758">
+        <v>111</v>
+      </c>
+      <c r="C758" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H758" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A759" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B759">
+        <v>56</v>
+      </c>
+      <c r="C759" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H759" s="1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A760" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B760">
+        <v>124</v>
+      </c>
+      <c r="C760" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H760" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A761" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B761">
+        <v>35</v>
+      </c>
+      <c r="C761" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H761" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A762" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B762">
+        <v>2</v>
+      </c>
+      <c r="C762" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H762" s="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A763" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B763">
+        <v>1</v>
+      </c>
+      <c r="C763" s="6" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H763" s="1">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A764" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B764">
+        <v>174</v>
+      </c>
+      <c r="C764" s="6" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H764" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A765" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B765">
+        <v>60</v>
+      </c>
+      <c r="C765" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H765" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A766" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B766">
+        <v>23</v>
+      </c>
+      <c r="C766" s="6" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H766" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A767" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B767">
+        <v>6</v>
+      </c>
+      <c r="C767" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="H767" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A768" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B768">
+        <v>1</v>
+      </c>
+      <c r="C768" s="6" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H768" s="1">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="769" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A769" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B769">
+        <v>3</v>
+      </c>
+      <c r="C769" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H769" s="1">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A770" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B770">
+        <v>70</v>
+      </c>
+      <c r="C770" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H770" s="1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A771" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B771">
+        <v>38</v>
+      </c>
+      <c r="C771" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H771" s="1">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A772" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B772">
+        <v>46</v>
+      </c>
+      <c r="C772" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H772" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A773" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B773">
+        <v>1</v>
+      </c>
+      <c r="C773" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H773" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A774" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B774">
+        <v>1</v>
+      </c>
+      <c r="C774" s="6" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H774" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A775" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B775">
+        <v>31</v>
+      </c>
+      <c r="C775" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H775" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A776" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B776">
+        <v>35</v>
+      </c>
+      <c r="C776" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H776" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A777" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B777">
+        <v>597</v>
+      </c>
+      <c r="C777" s="6" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H777" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A778" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B778">
+        <v>6</v>
+      </c>
+      <c r="C778" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H778" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A779" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B779">
+        <v>65</v>
+      </c>
+      <c r="C779" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="H779" s="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A780" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B780">
+        <v>1</v>
+      </c>
+      <c r="C780" s="6" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H780" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A781" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B781">
+        <v>106</v>
+      </c>
+      <c r="C781" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H781" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A782" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B782">
+        <v>50</v>
+      </c>
+      <c r="C782" s="6" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H782" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A783" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B783">
+        <v>1</v>
+      </c>
+      <c r="C783" s="6" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H783" s="1">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A784" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B784">
+        <v>21</v>
+      </c>
+      <c r="C784" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H784" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A785" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B785">
+        <v>5</v>
+      </c>
+      <c r="C785" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H785" s="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A786" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B786">
+        <v>25</v>
+      </c>
+      <c r="C786" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H786" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A787" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B787">
+        <v>10</v>
+      </c>
+      <c r="C787" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H787" s="1">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A788" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B788">
+        <v>14</v>
+      </c>
+      <c r="C788" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H788" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A789" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B789">
+        <v>11</v>
+      </c>
+      <c r="C789" s="6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H789" s="1">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A790" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B790">
+        <v>21</v>
+      </c>
+      <c r="C790" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H790" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A791" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B791">
+        <v>44</v>
+      </c>
+      <c r="C791" s="6" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H791" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A792" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B792">
+        <v>1</v>
+      </c>
+      <c r="C792" s="6" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H792" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A793" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B793">
+        <v>52</v>
+      </c>
+      <c r="C793" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H793" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A794" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B794">
+        <v>16</v>
+      </c>
+      <c r="C794" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H794" s="1">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A795" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B795">
+        <v>124</v>
+      </c>
+      <c r="C795" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H795" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A796" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B796">
+        <v>127</v>
+      </c>
+      <c r="C796" s="6" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H796" s="1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A797" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B797">
+        <v>1</v>
+      </c>
+      <c r="C797" s="6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H797" s="1">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A798" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B798">
+        <v>2</v>
+      </c>
+      <c r="C798" s="6" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H798" s="1">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A799" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B799">
+        <v>46</v>
+      </c>
+      <c r="C799" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H799" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A800" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B800">
+        <v>980</v>
+      </c>
+      <c r="C800" s="6" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H800" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A801" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B801">
+        <v>140</v>
+      </c>
+      <c r="C801" s="6" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H801" s="1">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A802" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B802">
+        <v>100</v>
+      </c>
+      <c r="C802" s="6" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H802" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A803" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B803">
+        <v>16</v>
+      </c>
+      <c r="C803" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H803" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A804" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B804">
+        <v>28</v>
+      </c>
+      <c r="C804" s="6" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H804" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A805" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B805">
+        <v>130</v>
+      </c>
+      <c r="C805" s="6" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H805" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A806" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B806">
+        <v>200</v>
+      </c>
+      <c r="C806" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H806" s="1">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A807" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B807">
+        <v>1</v>
+      </c>
+      <c r="C807" s="6" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H807" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A808" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B808">
+        <v>50</v>
+      </c>
+      <c r="C808" s="6" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H808" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="809" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A809" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B809">
+        <v>46</v>
+      </c>
+      <c r="C809" s="6" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H809" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="810" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A810" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B810">
+        <v>17</v>
+      </c>
+      <c r="C810" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H810" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="811" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A811" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B811">
+        <v>1</v>
+      </c>
+      <c r="C811" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H811" s="1">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="812" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A812" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B812">
+        <v>22</v>
+      </c>
+      <c r="C812" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H812" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="813" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A813" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B813">
+        <v>122</v>
+      </c>
+      <c r="C813" s="6" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H813" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="814" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A814" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B814">
+        <v>1</v>
+      </c>
+      <c r="C814" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H814" s="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="815" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A815" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B815">
+        <v>50</v>
+      </c>
+      <c r="C815" s="6" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H815" s="1">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="816" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A816" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B816">
+        <v>16</v>
+      </c>
+      <c r="C816" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H816" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="817" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A817" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B817">
+        <v>3</v>
+      </c>
+      <c r="C817" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H817" s="1">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="818" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A818" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B818">
+        <v>36</v>
+      </c>
+      <c r="C818" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="H818" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="819" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A819" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B819">
+        <v>29</v>
+      </c>
+      <c r="C819" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H819" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="820" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A820" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B820">
+        <v>2</v>
+      </c>
+      <c r="C820" s="6" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H820" s="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="821" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A821" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B821">
+        <v>24</v>
+      </c>
+      <c r="C821" s="6" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H821" s="1">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="822" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A822" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B822">
+        <v>30</v>
+      </c>
+      <c r="C822" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H822" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="823" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A823" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B823">
+        <v>12</v>
+      </c>
+      <c r="C823" s="6" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H823" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="824" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A824" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B824">
+        <v>23</v>
+      </c>
+      <c r="C824" s="6" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H824" s="1">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="825" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A825" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B825">
+        <v>12</v>
+      </c>
+      <c r="C825" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H825" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="826" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A826" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B826">
+        <v>25</v>
+      </c>
+      <c r="C826" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H826" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="827" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A827" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B827">
+        <v>5</v>
+      </c>
+      <c r="C827" s="6" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H827" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="828" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A828" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B828">
+        <v>33</v>
+      </c>
+      <c r="C828" s="6" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H828" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="829" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A829" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B829">
+        <v>100</v>
+      </c>
+      <c r="C829" s="6" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H829" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="830" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A830" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B830">
+        <v>5</v>
+      </c>
+      <c r="C830" s="6" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H830" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="831" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A831" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B831">
+        <v>1</v>
+      </c>
+      <c r="C831" s="6" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H831" s="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="832" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A832" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B832">
+        <v>17</v>
+      </c>
+      <c r="C832" s="6" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H832" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="833" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A833" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B833">
+        <v>25</v>
+      </c>
+      <c r="C833" s="6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H833" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="834" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A834" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B834">
+        <v>90</v>
+      </c>
+      <c r="C834" s="6" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H834" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="835" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A835" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B835">
+        <v>1</v>
+      </c>
+      <c r="C835" s="6" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H835" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="836" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A836" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B836">
+        <v>25</v>
+      </c>
+      <c r="C836" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H836" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="837" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A837" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B837">
+        <v>137</v>
+      </c>
+      <c r="C837" s="6" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H837" s="1">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="838" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A838" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B838">
+        <v>156</v>
+      </c>
+      <c r="C838" s="6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H838" s="1">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="839" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A839" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B839">
+        <v>3</v>
+      </c>
+      <c r="C839" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H839" s="1">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="840" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A840" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B840">
+        <v>1</v>
+      </c>
+      <c r="C840" s="6" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H840" s="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="841" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A841" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B841">
+        <v>35</v>
+      </c>
+      <c r="C841" s="6" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H841" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="842" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A842" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B842">
+        <v>550</v>
+      </c>
+      <c r="C842" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H842" s="1">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="843" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A843" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B843">
+        <v>38</v>
+      </c>
+      <c r="C843" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H843" s="1">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="844" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A844" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B844">
+        <v>40</v>
+      </c>
+      <c r="C844" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="H844" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="845" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A845" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B845">
+        <v>57</v>
+      </c>
+      <c r="C845" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H845" s="1">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="846" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A846" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B846">
+        <v>135</v>
+      </c>
+      <c r="C846" s="6" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H846" s="1">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="847" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A847" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B847">
+        <v>869</v>
+      </c>
+      <c r="C847" s="6" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H847" s="1">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="848" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A848" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B848">
+        <v>190</v>
+      </c>
+      <c r="C848" s="6" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H848" s="1">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="849" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A849" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B849">
+        <v>12</v>
+      </c>
+      <c r="C849" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H849" s="1">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="850" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A850" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B850">
+        <v>12</v>
+      </c>
+      <c r="C850" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H850" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="851" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A851" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B851">
+        <v>48</v>
+      </c>
+      <c r="C851" s="6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="H851" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="852" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A852" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B852">
+        <v>195</v>
+      </c>
+      <c r="C852" s="6" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H852" s="1">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="853" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A853" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B853">
+        <v>1</v>
+      </c>
+      <c r="C853" s="6" t="s">
+        <v>1315</v>
+      </c>
+      <c r="H853" s="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="854" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A854" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B854">
+        <v>1</v>
+      </c>
+      <c r="C854" s="6" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H854" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="855" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A855" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B855">
+        <v>20</v>
+      </c>
+      <c r="C855" s="6" t="s">
+        <v>1319</v>
+      </c>
+      <c r="H855" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="856" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A856" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B856">
+        <v>1</v>
+      </c>
+      <c r="C856" s="6" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H856" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="857" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A857" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B857">
+        <v>40</v>
+      </c>
+      <c r="C857" s="6" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H857" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="858" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A858" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B858">
+        <v>42</v>
+      </c>
+      <c r="C858" s="6" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H858" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="859" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A859" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B859">
+        <v>2</v>
+      </c>
+      <c r="C859" s="6" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H859" s="1">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="860" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A860" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B860">
+        <v>7</v>
+      </c>
+      <c r="C860" s="6" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H860" s="1">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="861" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A861" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B861">
+        <v>1</v>
+      </c>
+      <c r="C861" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H861" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="862" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A862" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B862">
+        <v>250</v>
+      </c>
+      <c r="C862" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H862" s="1">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="863" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A863" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B863">
+        <v>13</v>
+      </c>
+      <c r="C863" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H863" s="1">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="864" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A864" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B864">
+        <v>41</v>
+      </c>
+      <c r="C864" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H864" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="865" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A865" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B865">
+        <v>1</v>
+      </c>
+      <c r="C865" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H865" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="866" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A866" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B866">
+        <v>4</v>
+      </c>
+      <c r="C866" s="6" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H866" s="1">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="867" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A867" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B867">
+        <v>11</v>
+      </c>
+      <c r="C867" s="6" t="s">
+        <v>1250</v>
+      </c>
+      <c r="H867" s="1">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="868" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A868" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B868">
+        <v>210</v>
+      </c>
+      <c r="C868" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H868" s="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="869" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A869" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B869">
+        <v>6</v>
+      </c>
+      <c r="C869" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H869" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="870" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A870" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B870">
+        <v>10</v>
+      </c>
+      <c r="C870" s="6" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H870" s="1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="871" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A871" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B871">
+        <v>2</v>
+      </c>
+      <c r="C871" s="6" t="s">
+        <v>1349</v>
+      </c>
+      <c r="H871" s="1">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="872" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A872" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B872">
+        <v>33</v>
+      </c>
+      <c r="C872" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H872" s="1">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="873" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A873" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B873">
+        <v>1</v>
+      </c>
+      <c r="C873" s="6" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H873" s="1">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="874" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A874" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B874">
+        <v>5</v>
+      </c>
+      <c r="C874" s="6" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H874" s="1">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="875" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A875" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B875">
+        <v>30</v>
+      </c>
+      <c r="C875" s="6" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H875" s="1">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="876" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A876" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B876">
+        <v>5</v>
+      </c>
+      <c r="C876" s="6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H876" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="877" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A877" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B877">
+        <v>21</v>
+      </c>
+      <c r="C877" s="6" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H877" s="1">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="878" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A878" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B878">
+        <v>10</v>
+      </c>
+      <c r="C878" s="6" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H878" s="1">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="879" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A879" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B879">
+        <v>56</v>
+      </c>
+      <c r="C879" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H879" s="1">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="880" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A880" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B880">
+        <v>34</v>
+      </c>
+      <c r="C880" s="6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H880" s="1">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="881" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A881" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B881">
+        <v>1</v>
+      </c>
+      <c r="C881" s="6" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H881" s="1">
+        <v>1381</v>
       </c>
     </row>
   </sheetData>
